--- a/03_Data_Analysis/Sprint_05/Unidad_02_Procesado_Datos_Internos_Ficheros/02_Ejercicios_Workout/data/ejercicio_excel.xlsx
+++ b/03_Data_Analysis/Sprint_05/Unidad_02_Procesado_Datos_Internos_Ficheros/02_Ejercicios_Workout/data/ejercicio_excel.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,218 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>año</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>acontecimiento</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>lugar</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1993</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>La creación de la Unión Europea</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>La caída del Muro de Berlín</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Alemania</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>La primera ascensión al Everest</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nepal/China</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1949</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>La creación de la República Popular China</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1947</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>La independencia de la India</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1945</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>El final de la Segunda Guerra Mundial</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>el Mundo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1944</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>La invasión de Normandía durante la Segunda Guerra Mundial</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1928</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>El descubrimiento de la penicilina por Alexander Fleming</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Reino Unido</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1919</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>La firma del Tratado de Versalles</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1917</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>La Revolución Rusa</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rusia</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1914</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>El inicio de la Primera Guerra Mundial</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1912</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>El hundimiento del Titanic</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>el Atlántico Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1903</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>El primer vuelo de los hermanos Wright</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Estados Unidos</t>
         </is>
       </c>
     </row>
